--- a/gyno_camp/test_samples/test_camp_summary_single_and_multi_clinicians.xlsx
+++ b/gyno_camp/test_samples/test_camp_summary_single_and_multi_clinicians.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Generated At:</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-13 13:43</t>
+    <t xml:space="preserve">2026-10-13 15:10</t>
   </si>
   <si>
     <t xml:space="preserve"/>

--- a/gyno_camp/test_samples/test_camp_summary_single_and_multi_clinicians.xlsx
+++ b/gyno_camp/test_samples/test_camp_summary_single_and_multi_clinicians.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Generated At:</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-13 15:10</t>
+    <t xml:space="preserve">2026-10-13 15:40</t>
   </si>
   <si>
     <t xml:space="preserve"/>

--- a/gyno_camp/test_samples/test_camp_summary_single_and_multi_clinicians.xlsx
+++ b/gyno_camp/test_samples/test_camp_summary_single_and_multi_clinicians.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Generated At:</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-13 15:40</t>
+    <t xml:space="preserve">2026-10-13 16:49</t>
   </si>
   <si>
     <t xml:space="preserve"/>

--- a/gyno_camp/test_samples/test_camp_summary_single_and_multi_clinicians.xlsx
+++ b/gyno_camp/test_samples/test_camp_summary_single_and_multi_clinicians.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Generated At:</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-13 16:49</t>
+    <t xml:space="preserve">2026-10-15 12:41</t>
   </si>
   <si>
     <t xml:space="preserve"/>
